--- a/gaming_forms/013_esports_participation_inquiry--gaming_forms.xlsx
+++ b/gaming_forms/013_esports_participation_inquiry--gaming_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Player Interest</t>
+          <t>Are you interested in participating in esports events?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>team_details</t>
+          <t>player_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Team Details</t>
+          <t>Player Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>individual_details</t>
+          <t>team_details</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Individual Details</t>
+          <t>Team Details</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -597,11 +597,7 @@
           <t>Event Availability</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>When would you be available for an event?</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -611,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>event_availability</t>
+          <t>follow_up_preferences</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Event Availability</t>
+          <t>Follow-up Preferences</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,136 +630,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>follow_up_method</t>
+          <t>additional_details</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Follow up Method</t>
+          <t>Additional Details</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>follow_up_method</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Follow up Method</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>follow_up_method</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Follow up Method</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>follow_up_method</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Follow up Method</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>follow_up_method</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Follow up Method</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>follow_up_method</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Follow up Method</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -780,10 +661,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -834,210 +715,6 @@
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
